--- a/templates/Step7-偿付能力公司报告展示模块.xlsx
+++ b/templates/Step7-偿付能力公司报告展示模块.xlsx
@@ -1105,7 +1105,7 @@
       </c>
     </row>
     <row r="2" s="3">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>industry_premium_structure</t>
         </is>
@@ -1120,38 +1120,43 @@
           <t>规模与发展</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>行业整体保费规模与结构</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>行业保费规模与结构图</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>SIGNED_PREMIUM,SIGNED_PREMIUM_MOTOR</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>{"years":5,"annual_scope":"本年累计数"}</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>近五年行业保费合计及车险/非车险结构变化</t>
         </is>
       </c>
     </row>
     <row r="3" s="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>industry_market_share</t>
+        </is>
+      </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
           <t>行业概览</t>
@@ -1160,6 +1165,36 @@
       <c r="C3" s="0" t="inlineStr">
         <is>
           <t>市场份额</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>行业市场份额</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>行业市场份额图</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>SIGNED_PREMIUM,NET_PROFIT,COMBINED_RATIO</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>{"min_coverage":0.8}</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>最新年度按公司类别的保费、净利润、承保利润市场份额</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1226,12 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>COMBINED_RATIO,LOSS_RATIO,EXPENSE_RATIO</t>
+          <t>COMBINED_RATIO,SIGNED_PREMIUM</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>{"x_metric":"SIGNED_PREMIUM","x_label":"保费收入排名"}</t>
+          <t>{"years":5,"x_metric":"SIGNED_PREMIUM","x_label":"保费收入排名","breakeven":100}</t>
         </is>
       </c>
       <c r="H4" s="0" t="b">
@@ -1204,7 +1239,7 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>综合成本率、赔付率、费用率分布</t>
+          <t>近五年综合成本率与保费排名散点图（100% 盈亏平衡线），并汇总盈利/亏损公司数</t>
         </is>
       </c>
     </row>
@@ -1507,6 +1542,8 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19" customFormat="1" s="1">
       <c r="A19" s="1" t="inlineStr">
         <is>

--- a/templates/Step7-偿付能力公司报告展示模块.xlsx
+++ b/templates/Step7-偿付能力公司报告展示模块.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="163">
   <si>
     <t>模块ID</t>
   </si>
@@ -178,7 +178,7 @@
     <t>{"revenue_code":"SIGNED_PREMIUM","profit_code":"NET_PROFIT"}</t>
   </si>
   <si>
-    <t>solv_line_combined_ratio</t>
+    <t>combined_solvency_change</t>
   </si>
   <si>
     <t>核心指标速览</t>
@@ -187,46 +187,64 @@
     <t>综合偿付能力充足率</t>
   </si>
   <si>
+    <t>资本充足率组合图</t>
+  </si>
+  <si>
+    <t>ACTUAL_CAPITAL,MINIMUM_CAPITAL,COMBINED_SOLVENCY_RATIO</t>
+  </si>
+  <si>
+    <t>{"amount_groups":{"实际资本":["ACTUAL_CAPITAL"],"最低资本":["MINIMUM_CAPITAL"]},"grouped_amount_groups":{"实际资本":["ACTUAL_CAPITAL"],"最低资本":["MINIMUM_CAPITAL"]}}</t>
+  </si>
+  <si>
+    <t>上方 KPMG Pink 折线展示综合偿付能力充足率，下方堆叠柱展示实际资本与最低资本；按年度口径展示。</t>
+  </si>
+  <si>
+    <t>core_solvency_change</t>
+  </si>
+  <si>
+    <t>核心偿付能力充足率</t>
+  </si>
+  <si>
+    <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL,MINIMUM_CAPITAL,CORE_SOLVENCY_RATIO</t>
+  </si>
+  <si>
+    <t>{"amount_groups":{"核心资本":["CORE_T1_CAPITAL","CORE_T2_CAPITAL"],"最低资本":["MINIMUM_CAPITAL"]},"grouped_amount_groups":{"实际资本":["ACTUAL_CAPITAL"],"最低资本":["MINIMUM_CAPITAL"]}}</t>
+  </si>
+  <si>
+    <t>上方 KPMG Pink 折线展示核心偿付能力充足率，下方堆叠柱展示核心资本与最低资本；按年度口径展示。</t>
+  </si>
+  <si>
+    <t>core_capital_share</t>
+  </si>
+  <si>
+    <t>核心资本占比</t>
+  </si>
+  <si>
+    <t>资本结构组合图</t>
+  </si>
+  <si>
+    <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL,ANC_T1_CAPITAL,ANC_T2_CAPITAL,ACTUAL_CAPITAL</t>
+  </si>
+  <si>
+    <t>{"amount_groups":{"核心资本":["CORE_T1_CAPITAL","CORE_T2_CAPITAL"],"附属资本":["ANC_T1_CAPITAL","ANC_T2_CAPITAL"]}}</t>
+  </si>
+  <si>
+    <t>actual_capital_trend</t>
+  </si>
+  <si>
+    <t>偿付能力水平深度拆解</t>
+  </si>
+  <si>
+    <t>实际资本变动</t>
+  </si>
+  <si>
     <t>公司折线趋势图</t>
   </si>
   <si>
-    <t>COMBINED_SOLVENCY_RATIO</t>
-  </si>
-  <si>
-    <t>{}</t>
-  </si>
-  <si>
-    <t>各公司综合偿付能力充足率跨期走势（每家公司一个折线小图）</t>
-  </si>
-  <si>
-    <t>solv_line_core_ratio</t>
-  </si>
-  <si>
-    <t>核心偿付能力充足率</t>
-  </si>
-  <si>
-    <t>CORE_SOLVENCY_RATIO</t>
-  </si>
-  <si>
-    <t>各公司核心偿付能力充足率年度走势（每家公司一个折线小图，监管下限50%）</t>
-  </si>
-  <si>
-    <t>solv_line_invest_return</t>
-  </si>
-  <si>
-    <t>投资收益率</t>
-  </si>
-  <si>
-    <t>INVESTMENT_RETURN</t>
-  </si>
-  <si>
-    <t>各公司投资收益率（近三年平均）年度走势，每家公司一个折线小图</t>
-  </si>
-  <si>
-    <t>偿付能力水平深度拆解</t>
-  </si>
-  <si>
-    <t>实际资本变动</t>
+    <t>ACTUAL_CAPITAL</t>
+  </si>
+  <si>
+    <t>各公司实际资本年度变动走势，每家公司一个折线小图</t>
   </si>
   <si>
     <t>actual_to_recognized</t>
@@ -235,147 +253,171 @@
     <t>实际资本/认可资产率</t>
   </si>
   <si>
+    <t>ACTUAL_CAPITAL_TO_RECOGNIZED_ASSETS</t>
+  </si>
+  <si>
+    <t>各公司实际资本/认可资产率年度走势，每家公司一个折线小图</t>
+  </si>
+  <si>
+    <t>minimum_capital_trend</t>
+  </si>
+  <si>
+    <t>最低资本变动</t>
+  </si>
+  <si>
+    <t>MINIMUM_CAPITAL</t>
+  </si>
+  <si>
+    <t>各公司最低资本年度变动走势，每家公司一个折线小图</t>
+  </si>
+  <si>
+    <t>premium_growth_structure</t>
+  </si>
+  <si>
+    <t>经营与偿付能力联动分析</t>
+  </si>
+  <si>
+    <t>保费增速</t>
+  </si>
+  <si>
+    <t>保费增速结构图</t>
+  </si>
+  <si>
+    <t>{"years":5,"annual_scope":"本年累计数","total_code":"SIGNED_PREMIUM","motor_code":"SIGNED_PREMIUM_MOTOR"}</t>
+  </si>
+  <si>
+    <t>每家公司近五年车险/非车险结构占比与总保费同比增速</t>
+  </si>
+  <si>
+    <t>赔付率</t>
+  </si>
+  <si>
+    <t>费用率</t>
+  </si>
+  <si>
+    <t>投资利润</t>
+  </si>
+  <si>
+    <t>solv_overview</t>
+  </si>
+  <si>
+    <t>公司规模与结构</t>
+  </si>
+  <si>
+    <t>关键偿付数据概览</t>
+  </si>
+  <si>
+    <t>关键指标表</t>
+  </si>
+  <si>
+    <t>structure_change_1</t>
+  </si>
+  <si>
+    <t>行业画像</t>
+  </si>
+  <si>
+    <t>承保规模</t>
+  </si>
+  <si>
+    <t>结构变化组合图</t>
+  </si>
+  <si>
+    <t>SIGNED_PREMIUM_MOTOR,SIGNED_PREMIUM</t>
+  </si>
+  <si>
+    <t>structure_change_2</t>
+  </si>
+  <si>
+    <t>经营效益</t>
+  </si>
+  <si>
+    <t>NET_PROFIT,TOTAL_ASSETS</t>
+  </si>
+  <si>
+    <t>structure_change_3</t>
+  </si>
+  <si>
+    <t>资本规模</t>
+  </si>
+  <si>
+    <t>CORE_T1_CAPITAL,ANC_T1_CAPITAL,ACTUAL_CAPITAL</t>
+  </si>
+  <si>
+    <t>capital_amount_combo</t>
+  </si>
+  <si>
+    <t>实际资本数据对比-行业资本分级</t>
+  </si>
+  <si>
+    <t>资本规模与结构</t>
+  </si>
+  <si>
+    <t>资本金额堆叠</t>
+  </si>
+  <si>
+    <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL,ANC_T1_CAPITAL,ANC_T2_CAPITAL</t>
+  </si>
+  <si>
+    <t>core_capital_pending</t>
+  </si>
+  <si>
+    <t>实际资本数据对比-核心资本</t>
+  </si>
+  <si>
+    <t>核心资本明细占比</t>
+  </si>
+  <si>
+    <t>构成堆叠图</t>
+  </si>
+  <si>
+    <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL</t>
+  </si>
+  <si>
+    <t>{"denominator_code":"ACTUAL_CAPITAL","components":[{"code":"CORE_T1_CAPITAL","label":"核心一级资本","color":"#00B8F5"},{"code":"CORE_T2_CAPITAL","label":"核心二级资本","color":"#ACEAFF"}]}</t>
+  </si>
+  <si>
+    <t>anc_capital_pending</t>
+  </si>
+  <si>
+    <t>实际资本数据对比-附属资本</t>
+  </si>
+  <si>
+    <t>附属资本明细占比</t>
+  </si>
+  <si>
+    <t>ANC_T1_CAPITAL,ANC_T2_CAPITAL</t>
+  </si>
+  <si>
+    <t>{"denominator_code":"ACTUAL_CAPITAL","components":[{"code":"ANC_T1_CAPITAL","label":"附属一级资本","color":"#B497FF"},{"code":"ANC_T2_CAPITAL","label":"附属二级资本","color":"#7213EA"}]}</t>
+  </si>
+  <si>
+    <t>quant_risk_stack</t>
+  </si>
+  <si>
+    <t>最低资本数据对比-风险构成情况</t>
+  </si>
+  <si>
+    <t>量化风险最低资本构成</t>
+  </si>
+  <si>
+    <t>NON_LIFE_INSURANCE_RISK_CAPITAL,MARKET_RISK_CAPITAL,CREDIT_RISK_CAPITAL</t>
+  </si>
+  <si>
+    <t>{"denominator_code":"QUANT_RISK_CAPITAL","components":[{"code":"NON_LIFE_INSURANCE_RISK_CAPITAL","label":"保险风险（非寿）","color":"#00B8F5"},{"code":"MARKET_RISK_CAPITAL","label":"市场风险","color":"#FFA3DA"},{"code":"CREDIT_RISK_CAPITAL","label":"信用风险","color":"#B497FF"}]}</t>
+  </si>
+  <si>
+    <t>non_life_risk_liability</t>
+  </si>
+  <si>
+    <t>实际资本数据对比-保险风险</t>
+  </si>
+  <si>
+    <t>保险风险（非寿）/认可负债率</t>
+  </si>
+  <si>
     <t>单指标趋势图</t>
   </si>
   <si>
-    <t>ACTUAL_CAPITAL_TO_RECOGNIZED_ASSETS</t>
-  </si>
-  <si>
-    <t>最低资本变动</t>
-  </si>
-  <si>
-    <t>经营与偿付能力联动分析</t>
-  </si>
-  <si>
-    <t>保费增速</t>
-  </si>
-  <si>
-    <t>赔付率</t>
-  </si>
-  <si>
-    <t>费用率</t>
-  </si>
-  <si>
-    <t>投资利润</t>
-  </si>
-  <si>
-    <t>solv_overview</t>
-  </si>
-  <si>
-    <t>公司规模与结构</t>
-  </si>
-  <si>
-    <t>关键偿付数据概览</t>
-  </si>
-  <si>
-    <t>关键指标表</t>
-  </si>
-  <si>
-    <t>structure_change_1</t>
-  </si>
-  <si>
-    <t>行业画像</t>
-  </si>
-  <si>
-    <t>承保规模</t>
-  </si>
-  <si>
-    <t>结构变化组合图</t>
-  </si>
-  <si>
-    <t>SIGNED_PREMIUM_MOTOR,SIGNED_PREMIUM</t>
-  </si>
-  <si>
-    <t>structure_change_2</t>
-  </si>
-  <si>
-    <t>经营效益</t>
-  </si>
-  <si>
-    <t>NET_PROFIT,TOTAL_ASSETS</t>
-  </si>
-  <si>
-    <t>structure_change_3</t>
-  </si>
-  <si>
-    <t>资本规模</t>
-  </si>
-  <si>
-    <t>CORE_T1_CAPITAL,ANC_T1_CAPITAL,ACTUAL_CAPITAL</t>
-  </si>
-  <si>
-    <t>capital_amount_combo</t>
-  </si>
-  <si>
-    <t>实际资本数据对比-行业资本分级</t>
-  </si>
-  <si>
-    <t>资本规模与结构</t>
-  </si>
-  <si>
-    <t>资本金额堆叠</t>
-  </si>
-  <si>
-    <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL,ANC_T1_CAPITAL,ANC_T2_CAPITAL</t>
-  </si>
-  <si>
-    <t>core_capital_pending</t>
-  </si>
-  <si>
-    <t>实际资本数据对比-核心资本</t>
-  </si>
-  <si>
-    <t>核心资本明细占比</t>
-  </si>
-  <si>
-    <t>构成堆叠图</t>
-  </si>
-  <si>
-    <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL</t>
-  </si>
-  <si>
-    <t>{"denominator_code":"ACTUAL_CAPITAL","components":[{"code":"CORE_T1_CAPITAL","label":"核心一级资本","color":"#00B8F5"},{"code":"CORE_T2_CAPITAL","label":"核心二级资本","color":"#ACEAFF"}]}</t>
-  </si>
-  <si>
-    <t>anc_capital_pending</t>
-  </si>
-  <si>
-    <t>实际资本数据对比-附属资本</t>
-  </si>
-  <si>
-    <t>附属资本明细占比</t>
-  </si>
-  <si>
-    <t>ANC_T1_CAPITAL,ANC_T2_CAPITAL</t>
-  </si>
-  <si>
-    <t>{"denominator_code":"ACTUAL_CAPITAL","components":[{"code":"ANC_T1_CAPITAL","label":"附属一级资本","color":"#B497FF"},{"code":"ANC_T2_CAPITAL","label":"附属二级资本","color":"#7213EA"}]}</t>
-  </si>
-  <si>
-    <t>quant_risk_stack</t>
-  </si>
-  <si>
-    <t>最低资本数据对比-风险构成情况</t>
-  </si>
-  <si>
-    <t>量化风险最低资本构成</t>
-  </si>
-  <si>
-    <t>NON_LIFE_INSURANCE_RISK_CAPITAL,MARKET_RISK_CAPITAL,CREDIT_RISK_CAPITAL</t>
-  </si>
-  <si>
-    <t>{"denominator_code":"QUANT_RISK_CAPITAL","components":[{"code":"NON_LIFE_INSURANCE_RISK_CAPITAL","label":"保险风险（非寿）","color":"#00B8F5"},{"code":"MARKET_RISK_CAPITAL","label":"市场风险","color":"#FFA3DA"},{"code":"CREDIT_RISK_CAPITAL","label":"信用风险","color":"#B497FF"}]}</t>
-  </si>
-  <si>
-    <t>non_life_risk_liability</t>
-  </si>
-  <si>
-    <t>实际资本数据对比-保险风险</t>
-  </si>
-  <si>
-    <t>保险风险（非寿）/认可负债率</t>
-  </si>
-  <si>
     <t>NON_LIFE_INSURANCE_RISK_TO_LIABILITIES</t>
   </si>
   <si>
@@ -458,21 +500,6 @@
   </si>
   <si>
     <t>重大融资表</t>
-  </si>
-  <si>
-    <t>core_capital_share</t>
-  </si>
-  <si>
-    <t>核心资本占比</t>
-  </si>
-  <si>
-    <t>资本结构组合图</t>
-  </si>
-  <si>
-    <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL,ANC_T1_CAPITAL,ANC_T2_CAPITAL,ACTUAL_CAPITAL</t>
-  </si>
-  <si>
-    <t>{"amount_groups":{"核心资本":["CORE_T1_CAPITAL","CORE_T2_CAPITAL"],"附属资本":["ANC_T1_CAPITAL","ANC_T2_CAPITAL"]}}</t>
   </si>
   <si>
     <t>capital_efficiency_bubble</t>
@@ -668,13 +695,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1066,7 +1093,7 @@
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
@@ -1134,11 +1161,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1452,53 +1479,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="14.5454545454545" style="2" customWidth="1"/>
-    <col min="2" max="2" width="32.3636363636364" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.2727272727273" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14" style="2" customWidth="1"/>
+    <col min="1" max="1" width="14.5454545454545" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.3636363636364" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.2727272727273" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1664,7 +1691,7 @@
         <v>53</v>
       </c>
       <c r="H7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="s">
         <v>54</v>
@@ -1690,18 +1717,18 @@
         <v>57</v>
       </c>
       <c r="G8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
         <v>36</v>
@@ -1709,301 +1736,269 @@
       <c r="C9" t="s">
         <v>49</v>
       </c>
-      <c r="D9" t="s">
-        <v>60</v>
+      <c r="D9" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="H9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10"/>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" t="b">
         <v>0</v>
       </c>
-      <c r="I9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>actual_capital_trend</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>实际资本变动</t>
-        </is>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t>公司折线趋势图</t>
-        </is>
-      </c>
-      <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t>ACTUAL_CAPITAL</t>
-        </is>
-      </c>
-      <c r="I10" s="0" t="inlineStr">
-        <is>
-          <t>各公司实际资本年度变动走势，每家公司一个折线小图</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>actual_to_recognized</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t>偿付能力水平深度拆解</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>实际资本/认可资产率</t>
-        </is>
-      </c>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t>公司折线趋势图</t>
-        </is>
-      </c>
-      <c r="F11" s="0" t="inlineStr">
-        <is>
-          <t>ACTUAL_CAPITAL_TO_RECOGNIZED_ASSETS</t>
-        </is>
-      </c>
-      <c r="I11" s="0" t="inlineStr">
-        <is>
-          <t>各公司实际资本/认可资产率年度走势，每家公司一个折线小图</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>minimum_capital_trend</t>
-        </is>
-      </c>
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t>偿付能力水平深度拆解</t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t>最低资本变动</t>
-        </is>
-      </c>
-      <c r="E12" s="0" t="inlineStr">
-        <is>
-          <t>公司折线趋势图</t>
-        </is>
-      </c>
-      <c r="F12" s="0" t="inlineStr">
-        <is>
-          <t>MINIMUM_CAPITAL</t>
-        </is>
-      </c>
-      <c r="I12" s="0" t="inlineStr">
-        <is>
-          <t>各公司最低资本年度变动走势，每家公司一个折线小图</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>72</v>
+      <c r="I14" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="B15" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="B16" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:8">
-      <c r="A19" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H19" s="1" t="b">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="B17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="1"/>
+    <row r="20" spans="1:8">
+      <c r="A20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="3" t="b">
         <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
         <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E21" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
         <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E22" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F22" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F23" t="s">
-        <v>94</v>
-      </c>
-      <c r="H23" t="b">
-        <v>1</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F24" t="s">
-        <v>99</v>
-      </c>
-      <c r="G24" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E25" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="F25" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G25" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -2011,120 +2006,123 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E26" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="F26" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G26" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" t="s">
         <v>111</v>
       </c>
-      <c r="B27" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" t="s">
-        <v>112</v>
-      </c>
-      <c r="D27" t="s">
-        <v>113</v>
-      </c>
-      <c r="E27" t="s">
-        <v>67</v>
-      </c>
       <c r="F27" t="s">
-        <v>114</v>
+        <v>122</v>
+      </c>
+      <c r="G27" t="s">
+        <v>123</v>
       </c>
       <c r="H27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E28" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="F28" t="s">
-        <v>118</v>
-      </c>
-      <c r="G28" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="H28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E29" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="F29" t="s">
-        <v>122</v>
+        <v>132</v>
+      </c>
+      <c r="G29" t="s">
+        <v>133</v>
       </c>
       <c r="H29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E30" t="s">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="F30" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -2132,71 +2130,71 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" t="s">
         <v>127</v>
       </c>
-      <c r="D31" t="s">
-        <v>128</v>
-      </c>
-      <c r="E31" t="s">
-        <v>98</v>
-      </c>
       <c r="F31" t="s">
-        <v>129</v>
-      </c>
-      <c r="G31" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="H31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D32" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="E32" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="F32" t="s">
-        <v>133</v>
+        <v>143</v>
+      </c>
+      <c r="G32" t="s">
+        <v>144</v>
       </c>
       <c r="H32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" t="s">
         <v>127</v>
       </c>
-      <c r="D33" t="s">
-        <v>135</v>
-      </c>
-      <c r="E33" t="s">
-        <v>67</v>
-      </c>
       <c r="F33" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -2204,42 +2202,42 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B34" t="s">
-        <v>138</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D34" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="E34" t="s">
-        <v>141</v>
+        <v>127</v>
+      </c>
+      <c r="F34" t="s">
+        <v>150</v>
       </c>
       <c r="H34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>152</v>
+      </c>
+      <c r="C35" t="s">
+        <v>153</v>
       </c>
       <c r="D35" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="E35" t="s">
-        <v>144</v>
-      </c>
-      <c r="F35" t="s">
-        <v>145</v>
-      </c>
-      <c r="G35" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -2247,49 +2245,72 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" t="s">
+        <v>62</v>
+      </c>
+      <c r="F36" t="s">
         <v>63</v>
       </c>
-      <c r="D36" t="s">
-        <v>148</v>
-      </c>
-      <c r="E36" t="s">
-        <v>149</v>
-      </c>
-      <c r="F36" t="s">
-        <v>150</v>
+      <c r="G36" t="s">
+        <v>64</v>
       </c>
       <c r="H36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E37" t="s">
-        <v>67</v>
+        <v>158</v>
       </c>
       <c r="F37" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38"/>
-      <c r="B38"/>
-      <c r="C38"/>
-      <c r="D38"/>
+      <c r="A38" t="s">
+        <v>160</v>
+      </c>
+      <c r="B38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" t="s">
+        <v>161</v>
+      </c>
+      <c r="E38" t="s">
+        <v>127</v>
+      </c>
+      <c r="F38" t="s">
+        <v>162</v>
+      </c>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39"/>
+      <c r="B39"/>
+      <c r="C39"/>
+      <c r="D39"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates/Step7-偿付能力公司报告展示模块.xlsx
+++ b/templates/Step7-偿付能力公司报告展示模块.xlsx
@@ -1028,7 +1028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="14.5454545454545" customWidth="1" style="2" min="1" max="1"/>
@@ -1152,7 +1152,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>industry_market_share</t>
         </is>
@@ -1167,32 +1167,32 @@
           <t>市场份额</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>行业市场份额</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>行业市场份额图</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>SIGNED_PREMIUM,NET_PROFIT,COMBINED_RATIO</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>{"min_coverage":0.8}</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>最新年度按公司类别的保费、净利润、承保利润市场份额</t>
         </is>
@@ -1246,47 +1246,52 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>capability_radar</t>
+          <t>industry_solvency_overview</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>行业对标与趋势研判</t>
+          <t>行业概览</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>能力框架-横向对标</t>
+          <t>偿付能力披露整体情况</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>能力五边形</t>
+          <t>偿付能力披露整体情况</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>能力雷达图</t>
+          <t>偿付能力整体情况卡片</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>PREMIUM_GROWTH,ROE,TOTAL_ASSETS,ACTUAL_CAPITAL,COMBINED_SOLVENCY_RATIO</t>
+          <t>ACTUAL_CAPITAL,MINIMUM_CAPITAL,CORE_T1_CAPITAL,CORE_T2_CAPITAL,COMBINED_SOLVENCY_RATIO,CORE_SOLVENCY_RATIO</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>{"axes":[{"code":"PREMIUM_GROWTH","label":"保费增速","period":"本季度数","lower":-10,"upper":30},{"code":"ROE","label":"ROE","period":"本年累计数","lower":0,"upper":15},{"code":"TOTAL_ASSETS","label":"总资产","period":"本季度数","lower":100000,"upper":100000000},{"code":"ACTUAL_CAPITAL","label":"实际资本","period":"本季度末数","lower":50000,"upper":30000000},{"code":"COMBINED_SOLVENCY_RATIO","label":"偿付能力","period":"本季度末数","lower":100,"upper":350}]}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H5" s="0" t="b">
         <v>0</v>
       </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>按行业合计口径计算综合/核心偿付能力充足率，并展示实际资本与最低资本</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>performance_pattern_grid</t>
+          <t>capability_radar</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
@@ -1296,27 +1301,27 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>经营表现-横向对标</t>
+          <t>能力框架-横向对标</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>公司业绩展示</t>
+          <t>能力五边形</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>业绩模式分列图</t>
+          <t>能力雷达图</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>SIGNED_PREMIUM,NET_PROFIT</t>
+          <t>PREMIUM_GROWTH,ROE,TOTAL_ASSETS,ACTUAL_CAPITAL,COMBINED_SOLVENCY_RATIO</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>{"revenue_code":"SIGNED_PREMIUM","profit_code":"NET_PROFIT"}</t>
+          <t>{"axes":[{"code":"PREMIUM_GROWTH","label":"保费增速","period":"本季度数","lower":-10,"upper":30},{"code":"ROE","label":"ROE","period":"本年累计数","lower":0,"upper":15},{"code":"TOTAL_ASSETS","label":"总资产","period":"本季度数","lower":100000,"upper":100000000},{"code":"ACTUAL_CAPITAL","label":"实际资本","period":"本季度末数","lower":50000,"upper":30000000},{"code":"COMBINED_SOLVENCY_RATIO","label":"偿付能力","period":"本季度末数","lower":100,"upper":350}]}</t>
         </is>
       </c>
       <c r="H6" s="0" t="b">
@@ -1326,7 +1331,7 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>solv_line_combined_ratio</t>
+          <t>performance_pattern_grid</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
@@ -1336,53 +1341,75 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>核心指标速览</t>
+          <t>经营表现-横向对标</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>综合偿付能力充足率</t>
+          <t>公司业绩展示</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t>公司折线趋势图</t>
+          <t>业绩模式分列图</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>COMBINED_SOLVENCY_RATIO</t>
+          <t>SIGNED_PREMIUM,NET_PROFIT</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"revenue_code":"SIGNED_PREMIUM","profit_code":"NET_PROFIT"}</t>
         </is>
       </c>
       <c r="H7" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="I7" s="0" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>solv_line_combined_ratio</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>行业对标与趋势研判</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>核心指标速览</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>综合偿付能力充足率</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>公司折线趋势图</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>COMBINED_SOLVENCY_RATIO</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
         <is>
           <t>各公司综合偿付能力充足率跨期走势（每家公司一个折线小图）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="n"/>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>行业对标与趋势研判</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>核心指标速览</t>
-        </is>
-      </c>
-      <c r="D8" s="0" t="inlineStr">
-        <is>
-          <t>核心偿付能力充足率</t>
         </is>
       </c>
     </row>
@@ -1398,72 +1425,78 @@
           <t>核心指标速览</t>
         </is>
       </c>
-      <c r="D9" s="0" t="n"/>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>核心偿付能力充足率</t>
+        </is>
+      </c>
     </row>
     <row r="10">
+      <c r="A10" s="0" t="n"/>
       <c r="B10" s="0" t="inlineStr">
         <is>
+          <t>行业对标与趋势研判</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>核心指标速览</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="0" t="inlineStr">
+        <is>
           <t>偿付能力水平深度拆解</t>
         </is>
       </c>
-      <c r="C10" s="0" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>实际资本变动</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>actual_to_recognized</t>
         </is>
       </c>
-      <c r="B11" s="0" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>偿付能力水平深度拆解</t>
         </is>
       </c>
-      <c r="C11" s="0" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>实际资本/认可资产率</t>
         </is>
       </c>
-      <c r="D11" s="0" t="n"/>
-      <c r="E11" s="0" t="inlineStr">
+      <c r="D12" s="0" t="n"/>
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>单指标趋势图</t>
         </is>
       </c>
-      <c r="F11" s="0" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>ACTUAL_CAPITAL_TO_RECOGNIZED_ASSETS</t>
         </is>
       </c>
-      <c r="H11" s="0" t="b">
+      <c r="H12" s="0" t="b">
         <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t>偿付能力水平深度拆解</t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t>最低资本变动</t>
-        </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>经营与偿付能力联动分析</t>
+          <t>偿付能力水平深度拆解</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>保费增速</t>
+          <t>最低资本变动</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1508,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>赔付率</t>
+          <t>保费增速</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1520,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>费用率</t>
+          <t>赔付率</t>
         </is>
       </c>
     </row>
@@ -1499,78 +1532,57 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
+          <t>费用率</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>经营与偿付能力联动分析</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
           <t>投资利润</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19" customFormat="1" s="1">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="19" customFormat="1" s="1"/>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>solv_overview</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>公司规模与结构</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>关键偿付数据概览</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>关键偿付数据概览</t>
         </is>
       </c>
-      <c r="E19" s="1" t="inlineStr">
+      <c r="E20" s="1" t="inlineStr">
         <is>
           <t>关键指标表</t>
         </is>
       </c>
-      <c r="H19" s="1" t="b">
+      <c r="H20" s="1" t="b">
         <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="inlineStr">
-        <is>
-          <t>structure_change_1</t>
-        </is>
-      </c>
-      <c r="B20" s="0" t="inlineStr">
-        <is>
-          <t>行业画像</t>
-        </is>
-      </c>
-      <c r="C20" s="0" t="inlineStr">
-        <is>
-          <t>规模与发展</t>
-        </is>
-      </c>
-      <c r="D20" s="0" t="inlineStr">
-        <is>
-          <t>承保规模</t>
-        </is>
-      </c>
-      <c r="E20" s="0" t="inlineStr">
-        <is>
-          <t>结构变化组合图</t>
-        </is>
-      </c>
-      <c r="F20" s="0" t="inlineStr">
-        <is>
-          <t>SIGNED_PREMIUM_MOTOR,SIGNED_PREMIUM</t>
-        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t>structure_change_2</t>
+          <t>structure_change_1</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
@@ -1585,7 +1597,7 @@
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>经营效益</t>
+          <t>承保规模</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
@@ -1595,14 +1607,14 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>NET_PROFIT,TOTAL_ASSETS</t>
+          <t>SIGNED_PREMIUM_MOTOR,SIGNED_PREMIUM</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t>structure_change_3</t>
+          <t>structure_change_2</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
@@ -1617,7 +1629,7 @@
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>资本规模</t>
+          <t>经营效益</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
@@ -1627,49 +1639,46 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>CORE_T1_CAPITAL,ANC_T1_CAPITAL,ACTUAL_CAPITAL</t>
+          <t>NET_PROFIT,TOTAL_ASSETS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t>capital_amount_combo</t>
+          <t>structure_change_3</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>公司规模与结构</t>
+          <t>行业画像</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>实际资本数据对比-行业资本分级</t>
+          <t>规模与发展</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>资本规模与结构</t>
+          <t>资本规模</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>资本金额堆叠</t>
+          <t>结构变化组合图</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL,ANC_T1_CAPITAL,ANC_T2_CAPITAL</t>
-        </is>
-      </c>
-      <c r="H23" s="0" t="b">
-        <v>1</v>
+          <t>CORE_T1_CAPITAL,ANC_T1_CAPITAL,ACTUAL_CAPITAL</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t>core_capital_pending</t>
+          <t>capital_amount_combo</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
@@ -1679,37 +1688,32 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>实际资本数据对比-核心资本</t>
+          <t>实际资本数据对比-行业资本分级</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t>核心资本明细占比</t>
+          <t>资本规模与结构</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>构成堆叠图</t>
+          <t>资本金额堆叠</t>
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL</t>
-        </is>
-      </c>
-      <c r="G24" s="0" t="inlineStr">
-        <is>
-          <t>{"denominator_code":"ACTUAL_CAPITAL","components":[{"code":"CORE_T1_CAPITAL","label":"核心一级资本","color":"#00B8F5"},{"code":"CORE_T2_CAPITAL","label":"核心二级资本","color":"#ACEAFF"}]}</t>
+          <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL,ANC_T1_CAPITAL,ANC_T2_CAPITAL</t>
         </is>
       </c>
       <c r="H24" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t>anc_capital_pending</t>
+          <t>core_capital_pending</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
@@ -1719,12 +1723,12 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>实际资本数据对比-附属资本</t>
+          <t>实际资本数据对比-核心资本</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t>附属资本明细占比</t>
+          <t>核心资本明细占比</t>
         </is>
       </c>
       <c r="E25" s="0" t="inlineStr">
@@ -1734,12 +1738,12 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>ANC_T1_CAPITAL,ANC_T2_CAPITAL</t>
+          <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL</t>
         </is>
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>{"denominator_code":"ACTUAL_CAPITAL","components":[{"code":"ANC_T1_CAPITAL","label":"附属一级资本","color":"#B497FF"},{"code":"ANC_T2_CAPITAL","label":"附属二级资本","color":"#7213EA"}]}</t>
+          <t>{"denominator_code":"ACTUAL_CAPITAL","components":[{"code":"CORE_T1_CAPITAL","label":"核心一级资本","color":"#00B8F5"},{"code":"CORE_T2_CAPITAL","label":"核心二级资本","color":"#ACEAFF"}]}</t>
         </is>
       </c>
       <c r="H25" s="0" t="b">
@@ -1749,7 +1753,7 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t>quant_risk_stack</t>
+          <t>anc_capital_pending</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
@@ -1759,12 +1763,12 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>最低资本数据对比-风险构成情况</t>
+          <t>实际资本数据对比-附属资本</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t>量化风险最低资本构成</t>
+          <t>附属资本明细占比</t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr">
@@ -1774,22 +1778,22 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>NON_LIFE_INSURANCE_RISK_CAPITAL,MARKET_RISK_CAPITAL,CREDIT_RISK_CAPITAL</t>
+          <t>ANC_T1_CAPITAL,ANC_T2_CAPITAL</t>
         </is>
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>{"denominator_code":"QUANT_RISK_CAPITAL","components":[{"code":"NON_LIFE_INSURANCE_RISK_CAPITAL","label":"保险风险（非寿）","color":"#00B8F5"},{"code":"MARKET_RISK_CAPITAL","label":"市场风险","color":"#FFA3DA"},{"code":"CREDIT_RISK_CAPITAL","label":"信用风险","color":"#B497FF"}]}</t>
+          <t>{"denominator_code":"ACTUAL_CAPITAL","components":[{"code":"ANC_T1_CAPITAL","label":"附属一级资本","color":"#B497FF"},{"code":"ANC_T2_CAPITAL","label":"附属二级资本","color":"#7213EA"}]}</t>
         </is>
       </c>
       <c r="H26" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t>non_life_risk_liability</t>
+          <t>quant_risk_stack</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
@@ -1799,32 +1803,37 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>实际资本数据对比-保险风险</t>
+          <t>最低资本数据对比-风险构成情况</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>保险风险（非寿）/认可负债率</t>
+          <t>量化风险最低资本构成</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t>单指标趋势图</t>
+          <t>构成堆叠图</t>
         </is>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>NON_LIFE_INSURANCE_RISK_TO_LIABILITIES</t>
+          <t>NON_LIFE_INSURANCE_RISK_CAPITAL,MARKET_RISK_CAPITAL,CREDIT_RISK_CAPITAL</t>
+        </is>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>{"denominator_code":"QUANT_RISK_CAPITAL","components":[{"code":"NON_LIFE_INSURANCE_RISK_CAPITAL","label":"保险风险（非寿）","color":"#00B8F5"},{"code":"MARKET_RISK_CAPITAL","label":"市场风险","color":"#FFA3DA"},{"code":"CREDIT_RISK_CAPITAL","label":"信用风险","color":"#B497FF"}]}</t>
         </is>
       </c>
       <c r="H27" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t>market_risk_stack</t>
+          <t>non_life_risk_liability</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
@@ -1834,37 +1843,32 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>实际资本数据对比-市场风险</t>
+          <t>实际资本数据对比-保险风险</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>各类市场风险占比</t>
+          <t>保险风险（非寿）/认可负债率</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>构成堆叠图</t>
+          <t>单指标趋势图</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>INTEREST_RATE_RISK_CAPITAL,EQUITY_RISK_CAPITAL,REAL_ESTATE_RISK_CAPITAL,OVERSEAS_FIXED_INCOME_RISK_CAPITAL,OVERSEAS_EQUITY_RISK_CAPITAL,FOREIGN_EXCHANGE_RISK_CAPITAL,MARKET_RISK_DIVERSIFICATION_EFFECT,MARKET_RISK_CAPITAL</t>
-        </is>
-      </c>
-      <c r="G28" s="0" t="inlineStr">
-        <is>
-          <t>{"denominator_code":"MARKET_RISK_CAPITAL"}</t>
+          <t>NON_LIFE_INSURANCE_RISK_TO_LIABILITIES</t>
         </is>
       </c>
       <c r="H28" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t>interest_rate_to_assets</t>
+          <t>market_risk_stack</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
@@ -1879,27 +1883,32 @@
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>利率风险/认可资产率</t>
+          <t>各类市场风险占比</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>单指标趋势图</t>
+          <t>构成堆叠图</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
         <is>
-          <t>INTEREST_RATE_RISK_TO_ASSETS</t>
+          <t>INTEREST_RATE_RISK_CAPITAL,EQUITY_RISK_CAPITAL,REAL_ESTATE_RISK_CAPITAL,OVERSEAS_FIXED_INCOME_RISK_CAPITAL,OVERSEAS_EQUITY_RISK_CAPITAL,FOREIGN_EXCHANGE_RISK_CAPITAL,MARKET_RISK_DIVERSIFICATION_EFFECT,MARKET_RISK_CAPITAL</t>
+        </is>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>{"denominator_code":"MARKET_RISK_CAPITAL"}</t>
         </is>
       </c>
       <c r="H29" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t>equity_risk_to_assets</t>
+          <t>interest_rate_to_assets</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
@@ -1914,7 +1923,7 @@
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>权益价格风险/认可资产率</t>
+          <t>利率风险/认可资产率</t>
         </is>
       </c>
       <c r="E30" s="0" t="inlineStr">
@@ -1924,7 +1933,7 @@
       </c>
       <c r="F30" s="0" t="inlineStr">
         <is>
-          <t>EQUITY_RISK_TO_ASSETS</t>
+          <t>INTEREST_RATE_RISK_TO_ASSETS</t>
         </is>
       </c>
       <c r="H30" s="0" t="b">
@@ -1934,7 +1943,7 @@
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t>credit_risk_stack</t>
+          <t>equity_risk_to_assets</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
@@ -1944,37 +1953,32 @@
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>实际资本数据对比-信用风险</t>
+          <t>实际资本数据对比-市场风险</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>各类信用风险占比</t>
+          <t>权益价格风险/认可资产率</t>
         </is>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>构成堆叠图</t>
+          <t>单指标趋势图</t>
         </is>
       </c>
       <c r="F31" s="0" t="inlineStr">
         <is>
-          <t>SPREAD_RISK_CAPITAL,COUNTERPARTY_RISK_CAPITAL,CREDIT_RISK_DIVERSIFICATION_EFFECT,CREDIT_RISK_CAPITAL</t>
-        </is>
-      </c>
-      <c r="G31" s="0" t="inlineStr">
-        <is>
-          <t>{"denominator_code":"CREDIT_RISK_CAPITAL"}</t>
+          <t>EQUITY_RISK_TO_ASSETS</t>
         </is>
       </c>
       <c r="H31" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t>spread_risk_to_assets</t>
+          <t>credit_risk_stack</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
@@ -1989,27 +1993,32 @@
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>利差风险/认可资产率</t>
+          <t>各类信用风险占比</t>
         </is>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>单指标趋势图</t>
+          <t>构成堆叠图</t>
         </is>
       </c>
       <c r="F32" s="0" t="inlineStr">
         <is>
-          <t>SPREAD_RISK_TO_ASSETS</t>
+          <t>SPREAD_RISK_CAPITAL,COUNTERPARTY_RISK_CAPITAL,CREDIT_RISK_DIVERSIFICATION_EFFECT,CREDIT_RISK_CAPITAL</t>
+        </is>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>{"denominator_code":"CREDIT_RISK_CAPITAL"}</t>
         </is>
       </c>
       <c r="H32" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t>counterparty_risk_to_assets</t>
+          <t>spread_risk_to_assets</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
@@ -2024,7 +2033,7 @@
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>对手违约风险/认可资产率</t>
+          <t>利差风险/认可资产率</t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr">
@@ -2034,7 +2043,7 @@
       </c>
       <c r="F33" s="0" t="inlineStr">
         <is>
-          <t>COUNTERPARTY_RISK_TO_ASSETS</t>
+          <t>SPREAD_RISK_TO_ASSETS</t>
         </is>
       </c>
       <c r="H33" s="0" t="b">
@@ -2044,62 +2053,62 @@
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t>financing</t>
+          <t>counterparty_risk_to_assets</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>附录</t>
+          <t>公司规模与结构</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>重大融资信息</t>
+          <t>实际资本数据对比-信用风险</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t>增资发债信息统计</t>
+          <t>对手违约风险/认可资产率</t>
         </is>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>重大融资表</t>
+          <t>单指标趋势图</t>
+        </is>
+      </c>
+      <c r="F34" s="0" t="inlineStr">
+        <is>
+          <t>COUNTERPARTY_RISK_TO_ASSETS</t>
         </is>
       </c>
       <c r="H34" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t>core_capital_share</t>
+          <t>financing</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>偿付能力水平深度拆解</t>
+          <t>附录</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>重大融资信息</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t>核心资本占比</t>
+          <t>增资发债信息统计</t>
         </is>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>资本结构组合图</t>
-        </is>
-      </c>
-      <c r="F35" s="0" t="inlineStr">
-        <is>
-          <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL,ANC_T1_CAPITAL,ANC_T2_CAPITAL,ACTUAL_CAPITAL</t>
-        </is>
-      </c>
-      <c r="G35" s="0" t="inlineStr">
-        <is>
-          <t>{"amount_groups":{"核心资本":["CORE_T1_CAPITAL","CORE_T2_CAPITAL"],"附属资本":["ANC_T1_CAPITAL","ANC_T2_CAPITAL"]}}</t>
+          <t>重大融资表</t>
         </is>
       </c>
       <c r="H35" s="0" t="b">
@@ -2109,7 +2118,7 @@
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t>capital_efficiency_bubble</t>
+          <t>core_capital_share</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
@@ -2119,27 +2128,32 @@
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>资本使用效率与核心资本占比气泡图</t>
+          <t>核心资本占比</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>资本效率气泡图</t>
+          <t>资本结构组合图</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t>ACTUAL_CAPITAL,RECOGNIZED_ASSETS,REGISTERED_CAPITAL,CORE_T1_CAPITAL,CORE_T2_CAPITAL</t>
+          <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL,ANC_T1_CAPITAL,ANC_T2_CAPITAL,ACTUAL_CAPITAL</t>
+        </is>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t>{"amount_groups":{"核心资本":["CORE_T1_CAPITAL","CORE_T2_CAPITAL"],"附属资本":["ANC_T1_CAPITAL","ANC_T2_CAPITAL"]}}</t>
         </is>
       </c>
       <c r="H36" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t>core_capital_to_registered</t>
+          <t>capital_efficiency_bubble</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
@@ -2149,17 +2163,17 @@
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t>核心资本/注册资本</t>
+          <t>资本使用效率与核心资本占比气泡图</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>单指标趋势图</t>
+          <t>资本效率气泡图</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
         <is>
-          <t>CORE_CAPITAL_TO_REGISTERED_CAPITAL</t>
+          <t>ACTUAL_CAPITAL,RECOGNIZED_ASSETS,REGISTERED_CAPITAL,CORE_T1_CAPITAL,CORE_T2_CAPITAL</t>
         </is>
       </c>
       <c r="H37" s="0" t="b">
@@ -2167,10 +2181,40 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="0" t="n"/>
-      <c r="B38" s="0" t="n"/>
-      <c r="C38" s="0" t="n"/>
-      <c r="D38" s="0" t="n"/>
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>core_capital_to_registered</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>偿付能力水平深度拆解</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>核心资本/注册资本</t>
+        </is>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>单指标趋势图</t>
+        </is>
+      </c>
+      <c r="F38" s="0" t="inlineStr">
+        <is>
+          <t>CORE_CAPITAL_TO_REGISTERED_CAPITAL</t>
+        </is>
+      </c>
+      <c r="H38" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="n"/>
+      <c r="B39" s="0" t="n"/>
+      <c r="C39" s="0" t="n"/>
+      <c r="D39" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates/Step7-偿付能力公司报告展示模块.xlsx
+++ b/templates/Step7-偿付能力公司报告展示模块.xlsx
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>{"years":5,"x_metric":"SIGNED_PREMIUM","x_label":"保费收入排名","breakeven":100}</t>
+          <t>{"years":5,"x_metric":"SIGNED_PREMIUM","x_label":"签单保费排名","breakeven":100}</t>
         </is>
       </c>
       <c r="H4" s="0" t="b">

--- a/templates/Step7-偿付能力公司报告展示模块.xlsx
+++ b/templates/Step7-偿付能力公司报告展示模块.xlsx
@@ -548,18 +548,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -895,7 +889,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -919,16 +913,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8">
@@ -937,97 +931,100 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1844,31 +1841,31 @@
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:9">
-      <c r="A18" t="s">
+      <c r="A18" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H18" t="b">
+      <c r="H18" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="4" t="s">
         <v>116</v>
       </c>
     </row>

--- a/templates/Step7-偿付能力公司报告展示模块.xlsx
+++ b/templates/Step7-偿付能力公司报告展示模块.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="18350" windowHeight="7000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="14.5454545454545" customWidth="1" style="2" min="1" max="1"/>
@@ -1151,7 +1151,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>industry_market_share</t>
+          <t>industry_premium_by_line</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1161,44 +1161,37 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>市场份额</t>
+          <t>分险种保费收入</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>行业市场份额</t>
+          <t>分险种保费收入</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>行业市场份额图</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>SIGNED_PREMIUM,NET_PROFIT,COMBINED_RATIO</t>
+          <t>分险种保费收入图</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>{"min_coverage":0.8}</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+          <t>{"unit":"亿元"}</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="b">
+        <v>0</v>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>最新年度按公司类别的保费、净利润、承保利润市场份额</t>
+          <t>分险种展示原保险保费收入与同比增速（单位：亿元），合并为一张柱线组合图（车险用右轴、其他险种用左轴）并标注缺失年度。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>underwriting_efficiency</t>
+          <t>industry_market_share</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -1208,42 +1201,44 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>承保效益</t>
+          <t>市场份额</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>承保效益</t>
+          <t>行业市场份额</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>承保效益散点图</t>
+          <t>行业市场份额图</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>COMBINED_RATIO,SIGNED_PREMIUM</t>
+          <t>SIGNED_PREMIUM,NET_PROFIT,COMBINED_RATIO</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>{"years":5,"x_metric":"SIGNED_PREMIUM","x_label":"保费收入排名","breakeven":100}</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="b">
-        <v>0</v>
+          <t>{"min_coverage":0.8}</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>近五年综合成本率与保费排名散点图（100% 盈亏平衡线），并汇总盈利/亏损公司数</t>
+          <t>最新年度按公司类别的保费、净利润、承保利润市场份额</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>industry_solvency_overview</t>
+          <t>underwriting_efficiency</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1253,27 +1248,27 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>偿付能力披露整体情况</t>
+          <t>承保效益</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>偿付能力披露整体情况</t>
+          <t>承保效益</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>偿付能力整体情况卡片</t>
+          <t>承保效益散点图</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>ACTUAL_CAPITAL,MINIMUM_CAPITAL,CORE_T1_CAPITAL,CORE_T2_CAPITAL,COMBINED_SOLVENCY_RATIO,CORE_SOLVENCY_RATIO</t>
+          <t>COMBINED_RATIO,SIGNED_PREMIUM</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"years":5,"x_metric":"SIGNED_PREMIUM","x_label":"保费收入排名","breakeven":100}</t>
         </is>
       </c>
       <c r="H5" s="4" t="b">
@@ -1281,54 +1276,59 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>按行业合计口径计算综合/核心偿付能力充足率，并展示实际资本与最低资本</t>
+          <t>近五年综合成本率与保费排名散点图（100% 盈亏平衡线），并汇总盈利/亏损公司数</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>capability_radar</t>
+          <t>industry_solvency_overview</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>行业对标与趋势研判</t>
+          <t>行业概览</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>能力框架-横向对标</t>
+          <t>偿付能力披露整体情况</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>能力五边形</t>
+          <t>偿付能力披露整体情况</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>能力雷达图</t>
+          <t>偿付能力整体情况卡片</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>ACTUAL_CAPITAL,COMBINED_SOLVENCY_RATIO,ROE,COMBINED_RATIO,PREMIUM_GROWTH</t>
+          <t>ACTUAL_CAPITAL,MINIMUM_CAPITAL,CORE_T1_CAPITAL,CORE_T2_CAPITAL,COMBINED_SOLVENCY_RATIO,CORE_SOLVENCY_RATIO</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>{"axes": [{"code": "ACTUAL_CAPITAL", "label": "资本实力", "period": "本季度末数", "lower": 200000, "upper": 15000000}, {"code": "COMBINED_SOLVENCY_RATIO", "label": "偿付能力", "period": "本季度末数"}, {"code": "ROE", "label": "盈利能力", "period": "本年累计数", "lower": 0, "upper": 12}, {"code": "COMBINED_RATIO", "label": "承保风控能力", "period": "本年累计数", "scoring": "average", "lower_is_better": true, "average_center": 60, "average_span": 0.1}, {"code": "PREMIUM_GROWTH", "label": "业务拓展", "period": "本季度数", "lower": -10, "upper": 40}]}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H6" s="4" t="b">
         <v>0</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>按行业合计口径计算综合/核心偿付能力充足率，并展示实际资本与最低资本</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>performance_pattern_grid</t>
+          <t>capability_radar</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1338,27 +1338,27 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>经营表现-横向对标</t>
+          <t>能力框架-横向对标</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>公司业绩展示</t>
+          <t>能力五边形</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>业绩模式分列图</t>
+          <t>能力雷达图</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>SIGNED_PREMIUM,NET_PROFIT</t>
+          <t>ACTUAL_CAPITAL,COMBINED_SOLVENCY_RATIO,ROE,COMBINED_RATIO,PREMIUM_GROWTH</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>{"revenue_code":"SIGNED_PREMIUM","profit_code":"NET_PROFIT"}</t>
+          <t>{"axes": [{"code": "ACTUAL_CAPITAL", "label": "资本实力", "period": "本季度末数", "lower": 200000, "upper": 15000000}, {"code": "COMBINED_SOLVENCY_RATIO", "label": "偿付能力", "period": "本季度末数"}, {"code": "ROE", "label": "盈利能力", "period": "本年累计数", "lower": 0, "upper": 12}, {"code": "COMBINED_RATIO", "label": "承保风控能力", "period": "本年累计数", "scoring": "average", "lower_is_better": true, "average_center": 60, "average_span": 0.1}, {"code": "PREMIUM_GROWTH", "label": "业务拓展", "period": "本季度数", "lower": -10, "upper": 40}]}</t>
         </is>
       </c>
       <c r="H7" s="4" t="b">
@@ -1368,7 +1368,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>combined_solvency_change</t>
+          <t>performance_pattern_grid</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1378,42 +1378,37 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>核心指标速览</t>
+          <t>经营表现-横向对标</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>综合偿付能力充足率</t>
+          <t>公司业绩展示</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>资本充足率组合图</t>
+          <t>业绩模式分列图</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>ACTUAL_CAPITAL,MINIMUM_CAPITAL,COMBINED_SOLVENCY_RATIO</t>
+          <t>SIGNED_PREMIUM,NET_PROFIT</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>{"amount_groups":{"实际资本":["ACTUAL_CAPITAL"],"最低资本":["MINIMUM_CAPITAL"]},"grouped_amount_groups":{"实际资本":["ACTUAL_CAPITAL"],"最低资本":["MINIMUM_CAPITAL"]},"annual_labels":true,"year_start":2023,"year_end":2025}</t>
+          <t>{"revenue_code":"SIGNED_PREMIUM","profit_code":"NET_PROFIT"}</t>
         </is>
       </c>
       <c r="H8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>上方 KPMG Pink 折线展示综合偿付能力充足率，下方堆叠柱展示实际资本与最低资本；按年度口径展示。</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>core_solvency_change</t>
+          <t>combined_solvency_change</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1428,7 +1423,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>核心偿付能力充足率</t>
+          <t>综合偿付能力充足率</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1438,12 +1433,12 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL,MINIMUM_CAPITAL,CORE_SOLVENCY_RATIO</t>
+          <t>ACTUAL_CAPITAL,MINIMUM_CAPITAL,COMBINED_SOLVENCY_RATIO</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>{"amount_groups":{"核心资本":["CORE_T1_CAPITAL","CORE_T2_CAPITAL"],"最低资本":["MINIMUM_CAPITAL"]},"grouped_amount_groups":{"实际资本":["ACTUAL_CAPITAL"],"最低资本":["MINIMUM_CAPITAL"]},"annual_labels":true,"year_start":2023,"year_end":2025}</t>
+          <t>{"amount_groups":{"实际资本":["ACTUAL_CAPITAL"],"最低资本":["MINIMUM_CAPITAL"]},"grouped_amount_groups":{"实际资本":["ACTUAL_CAPITAL"],"最低资本":["MINIMUM_CAPITAL"]},"annual_labels":true,"year_start":2023,"year_end":2025}</t>
         </is>
       </c>
       <c r="H9" s="4" t="b">
@@ -1451,14 +1446,14 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>上方 KPMG Pink 折线展示核心偿付能力充足率，下方堆叠柱展示核心资本与最低资本；按年度口径展示。</t>
+          <t>上方 KPMG Pink 折线展示综合偿付能力充足率，下方堆叠柱展示实际资本与最低资本；按年度口径展示。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>core_capital_share</t>
+          <t>core_solvency_change</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1473,32 +1468,37 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>核心资本占比</t>
+          <t>核心偿付能力充足率</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>资本结构组合图</t>
+          <t>资本充足率组合图</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL,ANC_T1_CAPITAL,ANC_T2_CAPITAL,ACTUAL_CAPITAL</t>
+          <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL,MINIMUM_CAPITAL,CORE_SOLVENCY_RATIO</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>{"amount_groups":{"核心资本":["CORE_T1_CAPITAL","CORE_T2_CAPITAL"],"附属资本":["ANC_T1_CAPITAL","ANC_T2_CAPITAL"]},"annual_labels":true,"year_start":2023,"year_end":2025}</t>
+          <t>{"amount_groups":{"核心资本":["CORE_T1_CAPITAL","CORE_T2_CAPITAL"],"最低资本":["MINIMUM_CAPITAL"]},"grouped_amount_groups":{"实际资本":["ACTUAL_CAPITAL"],"最低资本":["MINIMUM_CAPITAL"]},"annual_labels":true,"year_start":2023,"year_end":2025}</t>
         </is>
       </c>
       <c r="H10" s="4" t="b">
         <v>1</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>上方 KPMG Pink 折线展示核心偿付能力充足率，下方堆叠柱展示核心资本与最低资本；按年度口径展示。</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>actual_capital_to_recognized_rate</t>
+          <t>core_capital_share</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1513,62 +1513,57 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>实际资本/认可资产率</t>
+          <t>核心资本占比</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>单指标趋势图</t>
+          <t>资本结构组合图</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>ACTUAL_CAPITAL_TO_RECOGNIZED_ASSETS</t>
+          <t>CORE_T1_CAPITAL,CORE_T2_CAPITAL,ANC_T1_CAPITAL,ANC_T2_CAPITAL,ACTUAL_CAPITAL</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>{"annual_labels":true,"year_start":2023,"year_end":2025}</t>
+          <t>{"amount_groups":{"核心资本":["CORE_T1_CAPITAL","CORE_T2_CAPITAL"],"附属资本":["ANC_T1_CAPITAL","ANC_T2_CAPITAL"]},"annual_labels":true,"year_start":2023,"year_end":2025}</t>
         </is>
       </c>
       <c r="H11" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>多公司实际资本/认可资产率跨期趋势对比。</t>
-        </is>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>capital_amount_combo</t>
+          <t>actual_capital_to_recognized_rate</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>偿付能力水平深度拆解</t>
+          <t>行业对标与趋势研判</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>实际资本变动</t>
+          <t>核心指标速览</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>资本金额堆叠</t>
+          <t>实际资本/认可资产率</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>资本金额堆叠</t>
+          <t>单指标趋势图</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>CORE_T1_CAPITAL,ANC_T1_CAPITAL</t>
+          <t>ACTUAL_CAPITAL_TO_RECOGNIZED_ASSETS</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1577,18 +1572,18 @@
         </is>
       </c>
       <c r="H12" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>100%堆叠柱展示核心一级、核心二级、附属一级和附属二级资本构成。</t>
+          <t>多公司实际资本/认可资产率跨期趋势对比。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>quant_risk_stack</t>
+          <t>capital_amount_combo</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1598,37 +1593,42 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>最低资本变动</t>
+          <t>实际资本变动</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>量化风险最低资本构成</t>
+          <t>资本金额堆叠</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>构成堆叠图</t>
+          <t>资本金额堆叠</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>NON_LIFE_INSURANCE_RISK_CAPITAL,MARKET_RISK_CAPITAL,CREDIT_RISK_CAPITAL,QUANT_RISK_DIVERSIFICATION_EFFECT</t>
+          <t>CORE_T1_CAPITAL,ANC_T1_CAPITAL</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>{"denominator_code":"QUANT_RISK_CAPITAL","components":[{"code":"NON_LIFE_INSURANCE_RISK_CAPITAL","label":"非寿险业务保险风险","color":"#00B8F5"},{"code":"MARKET_RISK_CAPITAL","label":"市场风险","color":"#FFA3DA"},{"code":"CREDIT_RISK_CAPITAL","label":"信用风险","color":"#B497FF"},{"code":"QUANT_RISK_DIVERSIFICATION_EFFECT","label":"风险分散","color":"#63EBB2"}],"annual_labels":true,"year_start":2023,"year_end":2025}</t>
+          <t>{"annual_labels":true,"year_start":2023,"year_end":2025}</t>
         </is>
       </c>
       <c r="H13" s="4" t="b">
         <v>1</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>100%堆叠柱展示核心一级、核心二级、附属一级和附属二级资本构成。</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>non_life_insurance_risk_component</t>
+          <t>quant_risk_stack</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>保险风险构成</t>
+          <t>量化风险最低资本构成</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1653,27 +1653,22 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>NON_LIFE_PREMIUM_RESERVE_RISK_CAPITAL,NON_LIFE_CATASTROPHE_RISK_CAPITAL,NON_LIFE_INSURANCE_RISK_DIVERSIFICATION_EFFECT</t>
+          <t>NON_LIFE_INSURANCE_RISK_CAPITAL,MARKET_RISK_CAPITAL,CREDIT_RISK_CAPITAL,QUANT_RISK_DIVERSIFICATION_EFFECT</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>{"denominator_code":"NON_LIFE_INSURANCE_RISK_CAPITAL","components":[{"code":"NON_LIFE_PREMIUM_RESERVE_RISK_CAPITAL","label":"保费及准备金风险","color":"#00B8F5"},{"code":"NON_LIFE_CATASTROPHE_RISK_CAPITAL","label":"巨灾风险","color":"#ACEAFF"},{"code":"NON_LIFE_INSURANCE_RISK_DIVERSIFICATION_EFFECT","label":"风险分散","color":"#63EBB2"}],"annual_labels":true,"year_start":2023,"year_end":2025}</t>
+          <t>{"denominator_code":"QUANT_RISK_CAPITAL","components":[{"code":"NON_LIFE_INSURANCE_RISK_CAPITAL","label":"非寿险业务保险风险","color":"#00B8F5"},{"code":"MARKET_RISK_CAPITAL","label":"市场风险","color":"#FFA3DA"},{"code":"CREDIT_RISK_CAPITAL","label":"信用风险","color":"#B497FF"},{"code":"QUANT_RISK_DIVERSIFICATION_EFFECT","label":"风险分散","color":"#63EBB2"}],"annual_labels":true,"year_start":2023,"year_end":2025}</t>
         </is>
       </c>
       <c r="H14" s="4" t="b">
         <v>1</v>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>非寿险业务保险风险构成：巨灾风险、准备金风险、保费风险和风险分散。</t>
-        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>non_life_insurance_risk_to_liabilities</t>
+          <t>non_life_insurance_risk_component</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1688,67 +1683,67 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>保险风险/认可负债率</t>
+          <t>保险风险构成</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>单指标趋势图</t>
+          <t>构成堆叠图</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>NON_LIFE_INSURANCE_RISK_TO_LIABILITIES</t>
+          <t>NON_LIFE_PREMIUM_RESERVE_RISK_CAPITAL,NON_LIFE_CATASTROPHE_RISK_CAPITAL,NON_LIFE_INSURANCE_RISK_DIVERSIFICATION_EFFECT</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>{"annual_labels":true,"year_start":2023,"year_end":2025}</t>
+          <t>{"denominator_code":"NON_LIFE_INSURANCE_RISK_CAPITAL","components":[{"code":"NON_LIFE_PREMIUM_RESERVE_RISK_CAPITAL","label":"保费及准备金风险","color":"#00B8F5"},{"code":"NON_LIFE_CATASTROPHE_RISK_CAPITAL","label":"巨灾风险","color":"#ACEAFF"},{"code":"NON_LIFE_INSURANCE_RISK_DIVERSIFICATION_EFFECT","label":"风险分散","color":"#63EBB2"}],"annual_labels":true,"year_start":2023,"year_end":2025}</t>
         </is>
       </c>
       <c r="H15" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>多公司保险风险/认可负债率跨期趋势对比。</t>
+          <t>非寿险业务保险风险构成：巨灾风险、准备金风险、保费风险和风险分散。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>premium_growth_structure</t>
+          <t>non_life_insurance_risk_to_liabilities</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>经营与偿付能力联动分析</t>
+          <t>偿付能力水平深度拆解</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>保费增速</t>
+          <t>最低资本变动</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>保费增速</t>
+          <t>保险风险/认可负债率</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>保费增速结构图</t>
+          <t>单指标趋势图</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>SIGNED_PREMIUM,SIGNED_PREMIUM_MOTOR</t>
+          <t>NON_LIFE_INSURANCE_RISK_TO_LIABILITIES</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>{"years":5,"annual_scope":"本年累计数","total_code":"SIGNED_PREMIUM","motor_code":"SIGNED_PREMIUM_MOTOR"}</t>
+          <t>{"annual_labels":true,"year_start":2023,"year_end":2025}</t>
         </is>
       </c>
       <c r="H16" s="4" t="b">
@@ -1756,14 +1751,14 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>每家公司近五年车险/非车险结构占比与总保费同比增速</t>
+          <t>多公司保险风险/认可负债率跨期趋势对比。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>loss_expense_cost_ratio</t>
+          <t>premium_growth_structure</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1773,27 +1768,27 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>赔付率&amp;费用率</t>
+          <t>保费增速</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>赔付率与费用率</t>
+          <t>保费增速</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>赔付费用率组合图</t>
+          <t>保费增速结构图</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>LOSS_RATIO,EXPENSE_RATIO,COMBINED_RATIO</t>
+          <t>SIGNED_PREMIUM,SIGNED_PREMIUM_MOTOR</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>{"years":5,"group_column":"同业分类"}</t>
+          <t>{"years":5,"annual_scope":"本年累计数","total_code":"SIGNED_PREMIUM","motor_code":"SIGNED_PREMIUM_MOTOR"}</t>
         </is>
       </c>
       <c r="H17" s="4" t="b">
@@ -1801,14 +1796,14 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>每家公司近五年赔付率、费用率堆叠及综合成本率变化。</t>
+          <t>每家公司近五年车险/非车险结构占比与总保费同比增速</t>
         </is>
       </c>
     </row>
     <row r="18" customFormat="1" s="4">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>investment_return_trend</t>
+          <t>loss_expense_cost_ratio</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1818,27 +1813,27 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>投资利润</t>
+          <t>赔付率&amp;费用率</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>投资收益率</t>
+          <t>赔付率与费用率</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>单指标趋势图</t>
+          <t>赔付费用率组合图</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>INVESTMENT_RETURN</t>
+          <t>LOSS_RATIO,EXPENSE_RATIO,COMBINED_RATIO</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>{"years":5,"annual_labels":true}</t>
+          <t>{"years":5,"group_column":"同业分类"}</t>
         </is>
       </c>
       <c r="H18" s="4" t="b">
@@ -1846,17 +1841,60 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
+          <t>每家公司近五年赔付率、费用率堆叠及综合成本率变化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>investment_return_trend</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>经营与偿付能力联动分析</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>投资利润</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>投资收益率</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>单指标趋势图</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>INVESTMENT_RETURN</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>{"years":5,"annual_labels":true}</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
           <t>各公司近五年投资收益率年度变动情况。</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
